--- a/docs/quarterly-accounts.xlsx
+++ b/docs/quarterly-accounts.xlsx
@@ -454,12 +454,10 @@
       <c r="C2">
         <f>B2*0.2</f>
         <v>290</v>
-        <v/>
       </c>
       <c r="D2">
         <f>B2+C2</f>
         <v>1740</v>
-        <v/>
       </c>
     </row>
     <row r="3">
@@ -474,12 +472,10 @@
       <c r="C3">
         <f>B3*0.2</f>
         <v>460</v>
-        <v/>
       </c>
       <c r="D3">
         <f>B3+C3</f>
         <v>2760</v>
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -494,12 +490,10 @@
       <c r="C4">
         <f>B4*0.2</f>
         <v>175</v>
-        <v/>
       </c>
       <c r="D4">
         <f>B4+C4</f>
         <v>1050</v>
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -514,12 +508,10 @@
       <c r="C5">
         <f>B5*0.2</f>
         <v>820</v>
-        <v/>
       </c>
       <c r="D5">
         <f>B5+C5</f>
         <v>4920</v>
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -534,12 +526,10 @@
       <c r="C6">
         <f>B6*0.2</f>
         <v>258</v>
-        <v/>
       </c>
       <c r="D6">
         <f>B6+C6</f>
         <v>1548</v>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -554,12 +544,10 @@
       <c r="C7">
         <f>B7*0.2</f>
         <v>735</v>
-        <v/>
       </c>
       <c r="D7">
         <f>B7+C7</f>
         <v>4410</v>
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -574,12 +562,10 @@
       <c r="C8">
         <f>B8*0.2</f>
         <v>190</v>
-        <v/>
       </c>
       <c r="D8">
         <f>B8+C8</f>
         <v>1140</v>
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -597,7 +583,6 @@
       <c r="D9">
         <f>B9+C9</f>
         <v>2726</v>
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -612,12 +597,10 @@
       <c r="C10">
         <f>B10*0.2</f>
         <v>226</v>
-        <v/>
       </c>
       <c r="D10">
         <f>B10+C10</f>
         <v>1356</v>
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -632,12 +615,10 @@
       <c r="C11">
         <f>B11*0.2</f>
         <v>1040</v>
-        <v/>
       </c>
       <c r="D11">
         <f>B11+C11</f>
         <v>6240</v>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -652,12 +633,10 @@
       <c r="C12">
         <f>B12*0.2</f>
         <v>156</v>
-        <v/>
       </c>
       <c r="D12">
         <f>B12+C12</f>
         <v>936</v>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -672,12 +651,10 @@
       <c r="C13">
         <f>B13*0.2</f>
         <v>668</v>
-        <v/>
       </c>
       <c r="D13">
         <f>B13+C13</f>
         <v>4008</v>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -692,12 +669,10 @@
       <c r="C14">
         <f>B14*0.2</f>
         <v>323</v>
-        <v/>
       </c>
       <c r="D14">
         <f>B14+C14</f>
         <v>1938</v>
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -712,12 +687,10 @@
       <c r="C15">
         <f>B15*0.2</f>
         <v>418</v>
-        <v/>
       </c>
       <c r="D15">
         <f>B15+C15</f>
         <v>2508</v>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -732,12 +705,10 @@
       <c r="C16">
         <f>B16*0.2</f>
         <v>188</v>
-        <v/>
       </c>
       <c r="D16">
         <f>B16+C16</f>
         <v>1128</v>
-        <v/>
       </c>
     </row>
     <row r="18">
@@ -749,17 +720,14 @@
       <c r="B18">
         <f>SUM(B2:B14)</f>
         <v>29185</v>
-        <v/>
       </c>
       <c r="C18">
         <f>SUM(C2:C16)</f>
         <v>6193</v>
-        <v/>
       </c>
       <c r="D18">
         <f>SUM(D2:D16)</f>
         <v>38408</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -803,7 +771,6 @@
       <c r="B4">
         <f>'Q3 Invoices'!B18</f>
         <v>29185</v>
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -815,7 +782,6 @@
       <c r="B5">
         <f>'Q3 Invoices'!C18</f>
         <v>6193</v>
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -827,7 +793,6 @@
       <c r="B6">
         <f>B4+B5</f>
         <v>33538</v>
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -866,7 +831,6 @@
       <c r="B11">
         <f>SUM(B9:B10)</f>
         <v>28250</v>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -888,7 +852,6 @@
       <c r="B13">
         <f>SUM(B9:B12)</f>
         <v>65800</v>
-        <v/>
       </c>
     </row>
     <row r="15">
